--- a/tests/fixtures/223111PE012_extrait_verite.xlsx
+++ b/tests/fixtures/223111PE012_extrait_verite.xlsx
@@ -9142,7 +9142,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une seule ligne au journal : « PAGE non imprimée dans tout le document : pages numérotées dans l'ordre »</t>
+          <t>PAGE non imprimée dans tout le document : pages numérotées dans l'ordre</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
